--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$92</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$101</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$86</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -4505,7 +4505,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4633,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.4, "op_wape_pct": 19.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 803.41, "rev_act": 746.57, "op_pred": 56.76, "op_act": 54.94}, {"q": "2025Q4", "rev_pred": 888.72, "rev_act": 769.58, "op_pred": 62.78, "op_act": 51.19}, {"q": "2026Q1", "rev_pred": 802.39, "rev_act": 763.36, "op_pred": 56.68, "op_act": 66.74}, {"q": "2026Q2", "rev_pred": 830.61, "rev_act": 882.14, "op_pred": 58.68, "op_act": 40.75}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 8.4, "op_wape_pct": 19.4, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": null, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 803.41, "rev_act": 746.57, "op_pred": 56.76, "op_act": 54.94}, {"q": "2025Q4", "rev_pred": 888.72, "rev_act": 769.58, "op_pred": 62.78, "op_act": 51.19}, {"q": "2026Q1", "rev_pred": 802.39, "rev_act": 763.36, "op_pred": 56.68, "op_act": 66.74}, {"q": "2026Q2", "rev_pred": 830.61, "rev_act": 882.14, "op_pred": 58.68, "op_act": 40.75}]}</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO92"/>
+  <dimension ref="A1:AO101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10509,7 +10509,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -15090,7 +15090,9 @@
       <c r="Z51" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="AB51" s="5" t="n"/>
+      <c r="AB51" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="11" t="n"/>
@@ -15213,18 +15215,11 @@
         <v>69981.25</v>
       </c>
       <c r="U53" s="9" t="n"/>
-      <c r="Y53" s="18" t="n">
-        <v>83961.72</v>
-      </c>
-      <c r="Z53" s="34" t="n">
-        <v>83961.72</v>
-      </c>
+      <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="18" t="n">
         <v>78598.02</v>
       </c>
-      <c r="AB53" s="19" t="n">
-        <v>83018.59</v>
-      </c>
+      <c r="AB53" s="5" t="n"/>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
       <c r="AE53" s="11" t="n"/>
@@ -17066,78 +17061,16 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="n">
-        <v>2644.37</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F75" s="9" t="n"/>
-      <c r="G75" s="18" t="n">
-        <v>4538.24</v>
-      </c>
-      <c r="H75" s="18" t="n">
-        <v>7960.46</v>
-      </c>
-      <c r="I75" s="18" t="n">
-        <v>21479.7</v>
-      </c>
-      <c r="J75" s="18" t="n">
-        <v>18130.93</v>
-      </c>
-      <c r="K75" s="34" t="n">
-        <v>52109.33</v>
-      </c>
-      <c r="L75" s="18" t="n">
-        <v>-4473.94</v>
-      </c>
-      <c r="M75" s="18" t="n">
-        <v>7289.36</v>
-      </c>
-      <c r="N75" s="18" t="n">
-        <v>16438.06</v>
-      </c>
-      <c r="O75" s="18" t="n">
-        <v>3265.98</v>
-      </c>
-      <c r="P75" s="34" t="n">
-        <v>22519.46</v>
-      </c>
-      <c r="Q75" s="18" t="n">
-        <v>4567.02</v>
-      </c>
-      <c r="R75" s="18" t="n">
-        <v>6895.99</v>
-      </c>
-      <c r="S75" s="18" t="n">
-        <v>2015.44</v>
-      </c>
-      <c r="T75" s="18" t="n">
-        <v>3363.79</v>
-      </c>
-      <c r="U75" s="34" t="n">
-        <v>16842.24</v>
-      </c>
-      <c r="V75" s="18" t="n">
-        <v>507.98</v>
-      </c>
-      <c r="W75" s="18" t="n">
-        <v>3777.18</v>
-      </c>
-      <c r="X75" s="18" t="n">
-        <v>5300.07</v>
-      </c>
-      <c r="Y75" s="18" t="n">
-        <v>10178.26</v>
-      </c>
-      <c r="Z75" s="34" t="n">
-        <v>19763.49</v>
-      </c>
-      <c r="AA75" s="18" t="n">
-        <v>9677.52</v>
-      </c>
+      <c r="K75" s="9" t="n"/>
+      <c r="P75" s="9" t="n"/>
+      <c r="U75" s="9" t="n"/>
+      <c r="Z75" s="9" t="n"/>
       <c r="AB75" s="19" t="n">
-        <v>-2742.16</v>
+        <v>325.57</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -17159,78 +17092,16 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="n">
-        <v>8.210000000000001</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F76" s="9" t="n"/>
-      <c r="G76" s="18" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H76" s="18" t="n">
-        <v>48.58</v>
-      </c>
-      <c r="I76" s="18" t="n">
-        <v>13.43</v>
-      </c>
-      <c r="J76" s="18" t="n">
-        <v>12.69</v>
-      </c>
-      <c r="K76" s="34" t="n">
-        <v>75.45</v>
-      </c>
-      <c r="L76" s="18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M76" s="18" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="N76" s="18" t="n">
-        <v>12.51</v>
-      </c>
-      <c r="O76" s="18" t="n">
-        <v>13.53</v>
-      </c>
-      <c r="P76" s="34" t="n">
-        <v>106.51</v>
-      </c>
-      <c r="Q76" s="18" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="R76" s="18" t="n">
-        <v>73.37</v>
-      </c>
-      <c r="S76" s="18" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="T76" s="18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U76" s="34" t="n">
-        <v>85.39</v>
-      </c>
-      <c r="V76" s="18" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="W76" s="18" t="n">
-        <v>562.63</v>
-      </c>
-      <c r="X76" s="18" t="n">
-        <v>31.27</v>
-      </c>
-      <c r="Y76" s="18" t="n">
-        <v>-96.61</v>
-      </c>
-      <c r="Z76" s="34" t="n">
-        <v>543.39</v>
-      </c>
-      <c r="AA76" s="18" t="n">
-        <v>22.39</v>
-      </c>
+      <c r="K76" s="9" t="n"/>
+      <c r="P76" s="9" t="n"/>
+      <c r="U76" s="9" t="n"/>
+      <c r="Z76" s="9" t="n"/>
       <c r="AB76" s="19" t="n">
-        <v>411.32</v>
+        <v>868.72</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -17252,78 +17123,16 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="n">
-        <v>-25.23</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F77" s="9" t="n"/>
-      <c r="G77" s="18" t="n">
-        <v>-984.76</v>
-      </c>
-      <c r="H77" s="18" t="n">
-        <v>-1261.15</v>
-      </c>
-      <c r="I77" s="18" t="n">
-        <v>-1257.41</v>
-      </c>
-      <c r="J77" s="18" t="n">
-        <v>-151.67</v>
-      </c>
-      <c r="K77" s="34" t="n">
-        <v>-3654.99</v>
-      </c>
-      <c r="L77" s="18" t="n">
-        <v>-3149.54</v>
-      </c>
-      <c r="M77" s="18" t="n">
-        <v>-3593.43</v>
-      </c>
-      <c r="N77" s="18" t="n">
-        <v>-1018.04</v>
-      </c>
-      <c r="O77" s="18" t="n">
-        <v>-1025.45</v>
-      </c>
-      <c r="P77" s="34" t="n">
-        <v>-8786.459999999999</v>
-      </c>
-      <c r="Q77" s="18" t="n">
-        <v>-49.46</v>
-      </c>
-      <c r="R77" s="18" t="n">
-        <v>-2149.89</v>
-      </c>
-      <c r="S77" s="18" t="n">
-        <v>-1580.68</v>
-      </c>
-      <c r="T77" s="18" t="n">
-        <v>-381.16</v>
-      </c>
-      <c r="U77" s="34" t="n">
-        <v>-4161.19</v>
-      </c>
-      <c r="V77" s="18" t="n">
-        <v>-1082.69</v>
-      </c>
-      <c r="W77" s="18" t="n">
-        <v>-1488.07</v>
-      </c>
-      <c r="X77" s="18" t="n">
-        <v>-1059.84</v>
-      </c>
-      <c r="Y77" s="18" t="n">
-        <v>2001.58</v>
-      </c>
-      <c r="Z77" s="34" t="n">
-        <v>-1629.02</v>
-      </c>
-      <c r="AA77" s="18" t="n">
-        <v>-180.09</v>
-      </c>
+      <c r="K77" s="9" t="n"/>
+      <c r="P77" s="9" t="n"/>
+      <c r="U77" s="9" t="n"/>
+      <c r="Z77" s="9" t="n"/>
       <c r="AB77" s="19" t="n">
-        <v>-2630.5</v>
+        <v>65.11</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -17345,78 +17154,16 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="n">
-        <v>2862.34</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F78" s="9" t="n"/>
-      <c r="G78" s="18" t="n">
-        <v>-10262.52</v>
-      </c>
-      <c r="H78" s="18" t="n">
-        <v>-47078.11</v>
-      </c>
-      <c r="I78" s="18" t="n">
-        <v>-5779.32</v>
-      </c>
-      <c r="J78" s="18" t="n">
-        <v>-21067.03</v>
-      </c>
-      <c r="K78" s="34" t="n">
-        <v>-84186.98</v>
-      </c>
-      <c r="L78" s="18" t="n">
-        <v>-2463.25</v>
-      </c>
-      <c r="M78" s="18" t="n">
-        <v>-1650.02</v>
-      </c>
-      <c r="N78" s="18" t="n">
-        <v>-4698.3</v>
-      </c>
-      <c r="O78" s="18" t="n">
-        <v>-4813.79</v>
-      </c>
-      <c r="P78" s="34" t="n">
-        <v>-13625.36</v>
-      </c>
-      <c r="Q78" s="18" t="n">
-        <v>-2559.25</v>
-      </c>
-      <c r="R78" s="18" t="n">
-        <v>-207.44</v>
-      </c>
-      <c r="S78" s="18" t="n">
-        <v>3075.97</v>
-      </c>
-      <c r="T78" s="18" t="n">
-        <v>-993.64</v>
-      </c>
-      <c r="U78" s="34" t="n">
-        <v>-684.36</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>-548.88</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>-622.13</v>
-      </c>
-      <c r="X78" s="18" t="n">
-        <v>-7884.88</v>
-      </c>
-      <c r="Y78" s="18" t="n">
-        <v>-14863.33</v>
-      </c>
-      <c r="Z78" s="34" t="n">
-        <v>-23919.22</v>
-      </c>
-      <c r="AA78" s="18" t="n">
-        <v>-5548.54</v>
-      </c>
+      <c r="K78" s="9" t="n"/>
+      <c r="P78" s="9" t="n"/>
+      <c r="U78" s="9" t="n"/>
+      <c r="Z78" s="9" t="n"/>
       <c r="AB78" s="19" t="n">
-        <v>-3764.48</v>
+        <v>-1.66</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -17438,78 +17185,16 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="n">
-        <v>7.39</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="G79" s="18" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="H79" s="18" t="n">
-        <v>7.02</v>
-      </c>
-      <c r="I79" s="18" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="J79" s="18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K79" s="34" t="n">
-        <v>84.81</v>
-      </c>
-      <c r="L79" s="18" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>16.62</v>
-      </c>
-      <c r="N79" s="18" t="n">
-        <v>94.73</v>
-      </c>
-      <c r="O79" s="18" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="P79" s="34" t="n">
-        <v>121.69</v>
-      </c>
-      <c r="Q79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R79" s="18" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="S79" s="18" t="n">
-        <v>5456.02</v>
-      </c>
-      <c r="T79" s="18" t="n">
-        <v>1393.13</v>
-      </c>
-      <c r="U79" s="34" t="n">
-        <v>6855.68</v>
-      </c>
-      <c r="V79" s="18" t="n">
-        <v>22.78</v>
-      </c>
-      <c r="W79" s="18" t="n">
-        <v>115.71</v>
-      </c>
-      <c r="X79" s="18" t="n">
-        <v>15.51</v>
-      </c>
-      <c r="Y79" s="18" t="n">
-        <v>1773.34</v>
-      </c>
-      <c r="Z79" s="34" t="n">
-        <v>1927.34</v>
-      </c>
-      <c r="AA79" s="18" t="n">
-        <v>49.85</v>
-      </c>
+      <c r="K79" s="9" t="n"/>
+      <c r="P79" s="9" t="n"/>
+      <c r="U79" s="9" t="n"/>
+      <c r="Z79" s="9" t="n"/>
       <c r="AB79" s="19" t="n">
-        <v>32.25</v>
+        <v>132.54</v>
       </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
@@ -17531,78 +17216,16 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>4205.25</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>8568.43</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>53721.53</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>7598.12</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>6242.36</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>76130.44</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>711.3099999999999</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>808.77</v>
-      </c>
-      <c r="N80" s="18" t="n">
-        <v>1221.29</v>
-      </c>
-      <c r="O80" s="18" t="n">
-        <v>1965.37</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>4706.74</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>4714.46</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>7896.3</v>
-      </c>
-      <c r="S80" s="18" t="n">
-        <v>4827.93</v>
-      </c>
-      <c r="T80" s="18" t="n">
-        <v>5193.73</v>
-      </c>
-      <c r="U80" s="34" t="n">
-        <v>22632.42</v>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>3275.96</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>2041.84</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>4746.57</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>7560.8</v>
-      </c>
-      <c r="Z80" s="34" t="n">
-        <v>17625.17</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>4006.33</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
+      <c r="P80" s="9" t="n"/>
+      <c r="U80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
       <c r="AB80" s="19" t="n">
-        <v>1655.08</v>
+        <v>266.64</v>
       </c>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
@@ -17624,78 +17247,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>4205.25</v>
+          <t>파생상품이익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>8568.43</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>53721.53</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>7598.12</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>6242.36</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>76130.44</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>711.3099999999999</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>808.77</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>1221.29</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>1965.37</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>4706.74</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>4714.46</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>7896.3</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>4827.93</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>5193.73</v>
-      </c>
-      <c r="U81" s="34" t="n">
-        <v>22632.42</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>3275.96</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>2041.84</v>
-      </c>
-      <c r="X81" s="18" t="n">
-        <v>4746.57</v>
-      </c>
-      <c r="Y81" s="18" t="n">
-        <v>7560.8</v>
-      </c>
-      <c r="Z81" s="34" t="n">
-        <v>17625.17</v>
-      </c>
-      <c r="AA81" s="18" t="n">
-        <v>4006.33</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
+      <c r="Z81" s="9" t="n"/>
       <c r="AB81" s="19" t="n">
-        <v>1655.08</v>
+        <v>-138.18</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -17717,78 +17278,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>4716.35</v>
+          <t>파생상품손실</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-1670.86</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>39160.88</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>-12326.39</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-258.81</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>24904.82</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-142.45</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-3448.12</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-5898.52</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-1932.02</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>-11421.11</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>-4312.73</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-2369.46</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-3383.22</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-5490.61</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-15556.02</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>822.4400000000001</v>
-      </c>
-      <c r="W82" s="18" t="n">
-        <v>4814.61</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>-3208.1</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>10600.17</v>
-      </c>
-      <c r="Z82" s="34" t="n">
-        <v>13029.12</v>
-      </c>
-      <c r="AA82" s="18" t="n">
-        <v>-3668.49</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
       <c r="AB82" s="19" t="n">
-        <v>1956</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -17810,78 +17309,16 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>35903.31</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>25080.7</v>
-      </c>
-      <c r="H83" s="18" t="n">
-        <v>49587.95</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>24313.12</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>16811.79</v>
-      </c>
-      <c r="K83" s="34" t="n">
-        <v>115793.56</v>
-      </c>
-      <c r="L83" s="18" t="n">
-        <v>38170.09</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>45012.32</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>13885.79</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>28973.09</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>126041.29</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>33877.28</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>44549.41</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>39577.06</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>41758.95</v>
-      </c>
-      <c r="U83" s="34" t="n">
-        <v>159762.7</v>
-      </c>
-      <c r="V83" s="18" t="n">
-        <v>43254.36</v>
-      </c>
-      <c r="W83" s="18" t="n">
-        <v>62537.5</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>38286.3</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>41720.63</v>
-      </c>
-      <c r="Z83" s="34" t="n">
-        <v>185798.79</v>
-      </c>
-      <c r="AA83" s="18" t="n">
-        <v>12615.31</v>
-      </c>
+      <c r="K83" s="9" t="n"/>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
+      <c r="Z83" s="9" t="n"/>
       <c r="AB83" s="19" t="n">
-        <v>58442.97</v>
+        <v>-543.15</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -17903,60 +17340,78 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>1009.17</v>
+        <v>2644.37</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>0</v>
+        <v>4538.24</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>37980</v>
+        <v>7960.46</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>0</v>
+        <v>21479.7</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>425.39</v>
+        <v>18130.93</v>
       </c>
       <c r="K84" s="34" t="n">
-        <v>38405.39</v>
+        <v>52109.33</v>
       </c>
       <c r="L84" s="18" t="n">
-        <v>26.4</v>
+        <v>-4473.94</v>
       </c>
       <c r="M84" s="18" t="n">
-        <v>92.59999999999999</v>
+        <v>7289.36</v>
+      </c>
+      <c r="N84" s="18" t="n">
+        <v>16438.06</v>
       </c>
       <c r="O84" s="18" t="n">
-        <v>850.95</v>
-      </c>
-      <c r="P84" s="9" t="n"/>
+        <v>3265.98</v>
+      </c>
+      <c r="P84" s="34" t="n">
+        <v>22519.46</v>
+      </c>
       <c r="Q84" s="18" t="n">
-        <v>7868.45</v>
+        <v>4567.02</v>
+      </c>
+      <c r="R84" s="18" t="n">
+        <v>6895.99</v>
+      </c>
+      <c r="S84" s="18" t="n">
+        <v>2015.44</v>
       </c>
       <c r="T84" s="18" t="n">
-        <v>1390.5</v>
-      </c>
-      <c r="U84" s="9" t="n"/>
+        <v>3363.79</v>
+      </c>
+      <c r="U84" s="34" t="n">
+        <v>16842.24</v>
+      </c>
       <c r="V84" s="18" t="n">
-        <v>448.12</v>
+        <v>507.98</v>
       </c>
       <c r="W84" s="18" t="n">
-        <v>1049.57</v>
+        <v>3777.18</v>
+      </c>
+      <c r="X84" s="18" t="n">
+        <v>5300.07</v>
       </c>
       <c r="Y84" s="18" t="n">
-        <v>2855.68</v>
-      </c>
-      <c r="Z84" s="9" t="n"/>
+        <v>10178.26</v>
+      </c>
+      <c r="Z84" s="34" t="n">
+        <v>19763.49</v>
+      </c>
       <c r="AA84" s="18" t="n">
-        <v>10424.53</v>
+        <v>9677.52</v>
       </c>
       <c r="AB84" s="19" t="n">
-        <v>264.77</v>
+        <v>-2742.16</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -17978,78 +17433,78 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>배당금수취(CF)</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>29610.48</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>22198.03</v>
+        <v>0.75</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>45469.65</v>
+        <v>48.58</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>33308.31</v>
+        <v>13.43</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>13492.38</v>
+        <v>12.69</v>
       </c>
       <c r="K85" s="34" t="n">
-        <v>114468.37</v>
+        <v>75.45</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>34146.04</v>
+        <v>1.02</v>
       </c>
       <c r="M85" s="18" t="n">
-        <v>46627.27</v>
+        <v>79.45</v>
       </c>
       <c r="N85" s="18" t="n">
-        <v>15474.67</v>
+        <v>12.51</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>28606.31</v>
+        <v>13.53</v>
       </c>
       <c r="P85" s="34" t="n">
-        <v>124854.29</v>
+        <v>106.51</v>
       </c>
       <c r="Q85" s="18" t="n">
-        <v>40605.81</v>
+        <v>0.08</v>
       </c>
       <c r="R85" s="18" t="n">
-        <v>42783.88</v>
+        <v>73.37</v>
       </c>
       <c r="S85" s="18" t="n">
-        <v>40724.04</v>
+        <v>9.67</v>
       </c>
       <c r="T85" s="18" t="n">
-        <v>45413.19</v>
+        <v>2.27</v>
       </c>
       <c r="U85" s="34" t="n">
-        <v>169526.92</v>
+        <v>85.39</v>
       </c>
       <c r="V85" s="18" t="n">
-        <v>37121.93</v>
+        <v>46.1</v>
       </c>
       <c r="W85" s="18" t="n">
-        <v>56112.25</v>
+        <v>562.63</v>
       </c>
       <c r="X85" s="18" t="n">
-        <v>39784.46</v>
+        <v>31.27</v>
       </c>
       <c r="Y85" s="18" t="n">
-        <v>33840.8</v>
+        <v>-96.61</v>
       </c>
       <c r="Z85" s="34" t="n">
-        <v>166859.44</v>
+        <v>543.39</v>
       </c>
       <c r="AA85" s="18" t="n">
-        <v>22701.02</v>
+        <v>22.39</v>
       </c>
       <c r="AB85" s="19" t="n">
-        <v>56719.77</v>
+        <v>411.32</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -18071,78 +17526,78 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>0</v>
+        <v>-25.23</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>800</v>
+        <v>-984.76</v>
       </c>
       <c r="H86" s="18" t="n">
-        <v>0</v>
+        <v>-1261.15</v>
       </c>
       <c r="I86" s="18" t="n">
-        <v>0</v>
+        <v>-1257.41</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>0</v>
+        <v>-151.67</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>800</v>
+        <v>-3654.99</v>
       </c>
       <c r="L86" s="18" t="n">
-        <v>960</v>
+        <v>-3149.54</v>
       </c>
       <c r="M86" s="18" t="n">
-        <v>0</v>
+        <v>-3593.43</v>
       </c>
       <c r="N86" s="18" t="n">
-        <v>0</v>
+        <v>-1018.04</v>
       </c>
       <c r="O86" s="18" t="n">
-        <v>0</v>
+        <v>-1025.45</v>
       </c>
       <c r="P86" s="34" t="n">
-        <v>960</v>
+        <v>-8786.459999999999</v>
       </c>
       <c r="Q86" s="18" t="n">
-        <v>960</v>
+        <v>-49.46</v>
       </c>
       <c r="R86" s="18" t="n">
-        <v>0</v>
+        <v>-2149.89</v>
       </c>
       <c r="S86" s="18" t="n">
-        <v>0</v>
+        <v>-1580.68</v>
       </c>
       <c r="T86" s="18" t="n">
-        <v>0</v>
+        <v>-381.16</v>
       </c>
       <c r="U86" s="34" t="n">
-        <v>960</v>
+        <v>-4161.19</v>
       </c>
       <c r="V86" s="18" t="n">
-        <v>1120</v>
+        <v>-1082.69</v>
       </c>
       <c r="W86" s="18" t="n">
-        <v>482.82</v>
+        <v>-1488.07</v>
       </c>
       <c r="X86" s="18" t="n">
-        <v>0</v>
+        <v>-1059.84</v>
       </c>
       <c r="Y86" s="18" t="n">
-        <v>0</v>
+        <v>2001.58</v>
       </c>
       <c r="Z86" s="34" t="n">
-        <v>1602.82</v>
+        <v>-1629.02</v>
       </c>
       <c r="AA86" s="18" t="n">
-        <v>4000</v>
+        <v>-180.09</v>
       </c>
       <c r="AB86" s="19" t="n">
-        <v>0</v>
+        <v>-2630.5</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -18164,54 +17619,78 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
-        <v>50.29</v>
+        <v>2862.34</v>
       </c>
       <c r="F87" s="9" t="n"/>
       <c r="G87" s="18" t="n">
-        <v>75.59999999999999</v>
+        <v>-10262.52</v>
       </c>
       <c r="H87" s="18" t="n">
-        <v>62.67</v>
+        <v>-47078.11</v>
       </c>
       <c r="I87" s="18" t="n">
-        <v>52.1</v>
+        <v>-5779.32</v>
       </c>
       <c r="J87" s="18" t="n">
-        <v>27.59</v>
+        <v>-21067.03</v>
       </c>
       <c r="K87" s="34" t="n">
-        <v>217.96</v>
+        <v>-84186.98</v>
       </c>
       <c r="L87" s="18" t="n">
-        <v>26.18</v>
+        <v>-2463.25</v>
       </c>
       <c r="M87" s="18" t="n">
-        <v>27.45</v>
-      </c>
-      <c r="P87" s="9" t="n"/>
+        <v>-1650.02</v>
+      </c>
+      <c r="N87" s="18" t="n">
+        <v>-4698.3</v>
+      </c>
+      <c r="O87" s="18" t="n">
+        <v>-4813.79</v>
+      </c>
+      <c r="P87" s="34" t="n">
+        <v>-13625.36</v>
+      </c>
       <c r="Q87" s="18" t="n">
-        <v>27.69</v>
+        <v>-2559.25</v>
       </c>
       <c r="R87" s="18" t="n">
-        <v>29.08</v>
-      </c>
-      <c r="U87" s="9" t="n"/>
+        <v>-207.44</v>
+      </c>
+      <c r="S87" s="18" t="n">
+        <v>3075.97</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>-993.64</v>
+      </c>
+      <c r="U87" s="34" t="n">
+        <v>-684.36</v>
+      </c>
       <c r="V87" s="18" t="n">
-        <v>30.53</v>
+        <v>-548.88</v>
       </c>
       <c r="W87" s="18" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="Z87" s="9" t="n"/>
+        <v>-622.13</v>
+      </c>
+      <c r="X87" s="18" t="n">
+        <v>-7884.88</v>
+      </c>
+      <c r="Y87" s="18" t="n">
+        <v>-14863.33</v>
+      </c>
+      <c r="Z87" s="34" t="n">
+        <v>-23919.22</v>
+      </c>
       <c r="AA87" s="18" t="n">
-        <v>30.5</v>
+        <v>-5548.54</v>
       </c>
       <c r="AB87" s="19" t="n">
-        <v>31.97</v>
+        <v>-3764.48</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -18233,78 +17712,78 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
-        <v>10652.53</v>
+        <v>7.39</v>
       </c>
       <c r="F88" s="9" t="n"/>
       <c r="G88" s="18" t="n">
-        <v>-7395.14</v>
+        <v>2.79</v>
       </c>
       <c r="H88" s="18" t="n">
-        <v>43.23</v>
+        <v>7.02</v>
       </c>
       <c r="I88" s="18" t="n">
-        <v>3373.99</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="J88" s="18" t="n">
-        <v>-3221.34</v>
+        <v>1.6</v>
       </c>
       <c r="K88" s="34" t="n">
-        <v>-7199.26</v>
+        <v>84.81</v>
       </c>
       <c r="L88" s="18" t="n">
-        <v>-7079.64</v>
+        <v>0.6</v>
       </c>
       <c r="M88" s="18" t="n">
-        <v>2191.22</v>
+        <v>16.62</v>
       </c>
       <c r="N88" s="18" t="n">
-        <v>5841.24</v>
+        <v>94.73</v>
       </c>
       <c r="O88" s="18" t="n">
-        <v>-3482.45</v>
+        <v>9.74</v>
       </c>
       <c r="P88" s="34" t="n">
-        <v>-2529.63</v>
+        <v>121.69</v>
       </c>
       <c r="Q88" s="18" t="n">
-        <v>-2304.96</v>
+        <v>0</v>
       </c>
       <c r="R88" s="18" t="n">
-        <v>4319.09</v>
+        <v>6.53</v>
       </c>
       <c r="S88" s="18" t="n">
-        <v>1708.19</v>
+        <v>5456.02</v>
       </c>
       <c r="T88" s="18" t="n">
-        <v>-2864.64</v>
+        <v>1393.13</v>
       </c>
       <c r="U88" s="34" t="n">
-        <v>857.6799999999999</v>
+        <v>6855.68</v>
       </c>
       <c r="V88" s="18" t="n">
-        <v>781.54</v>
+        <v>22.78</v>
       </c>
       <c r="W88" s="18" t="n">
-        <v>7969.66</v>
+        <v>115.71</v>
       </c>
       <c r="X88" s="18" t="n">
-        <v>-5792.91</v>
+        <v>15.51</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>5761.56</v>
+        <v>1773.34</v>
       </c>
       <c r="Z88" s="34" t="n">
-        <v>8719.85</v>
+        <v>1927.34</v>
       </c>
       <c r="AA88" s="18" t="n">
-        <v>737.0700000000001</v>
+        <v>49.85</v>
       </c>
       <c r="AB88" s="19" t="n">
-        <v>-4827.22</v>
+        <v>32.25</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -18326,78 +17805,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>10336.21</v>
+        <v>4205.25</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>8499.120000000001</v>
+        <v>8568.43</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>278.77</v>
+        <v>53721.53</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>3674.61</v>
+        <v>7598.12</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>-3796.73</v>
+        <v>6242.36</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>8655.77</v>
+        <v>76130.44</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>1695.22</v>
+        <v>711.3099999999999</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>2166.35</v>
+        <v>808.77</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>5846.85</v>
+        <v>1221.29</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>-3582.29</v>
+        <v>1965.37</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>6126.13</v>
+        <v>4706.74</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>3892.15</v>
+        <v>4714.46</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>4301.16</v>
+        <v>7896.3</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>1681.46</v>
+        <v>4827.93</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>-2890.96</v>
+        <v>5193.73</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>6983.81</v>
+        <v>22632.42</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>7769.05</v>
+        <v>3275.96</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>7670.13</v>
+        <v>2041.84</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>-5652.81</v>
+        <v>4746.57</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>5917.29</v>
+        <v>7560.8</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>15703.66</v>
+        <v>17625.17</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>16440.73</v>
+        <v>4006.33</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>-4591.33</v>
+        <v>1655.08</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -18419,70 +17898,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
-        </is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="n">
+        <v>4205.25</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>3677.92</v>
+        <v>8568.43</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>1819.2</v>
+        <v>53721.53</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>112.42</v>
+        <v>7598.12</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>20.43</v>
+        <v>6242.36</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>5629.97</v>
+        <v>76130.44</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>711.3099999999999</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>0</v>
+        <v>808.77</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>0</v>
+        <v>1221.29</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>1965.37</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>0</v>
+        <v>4706.74</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>1296.7</v>
+        <v>4714.46</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>902.0700000000001</v>
+        <v>7896.3</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>0</v>
+        <v>4827.93</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>12.19</v>
+        <v>5193.73</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>2210.96</v>
+        <v>22632.42</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>1458.97</v>
+        <v>3275.96</v>
+      </c>
+      <c r="W90" s="18" t="n">
+        <v>2041.84</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>1369.53</v>
+        <v>4746.57</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="Z90" s="9" t="n"/>
+        <v>7560.8</v>
+      </c>
+      <c r="Z90" s="34" t="n">
+        <v>17625.17</v>
+      </c>
       <c r="AA90" s="18" t="n">
-        <v>0</v>
+        <v>4006.33</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>0</v>
+        <v>1655.08</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -18504,67 +17991,78 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
-        </is>
+          <t>재무활동으로인한현금흐름</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="n">
+        <v>4716.35</v>
       </c>
       <c r="F91" s="9" t="n"/>
+      <c r="G91" s="18" t="n">
+        <v>-1670.86</v>
+      </c>
+      <c r="H91" s="18" t="n">
+        <v>39160.88</v>
+      </c>
       <c r="I91" s="18" t="n">
-        <v>3166.68</v>
+        <v>-12326.39</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>4222.24</v>
-      </c>
-      <c r="K91" s="9" t="n"/>
+        <v>-258.81</v>
+      </c>
+      <c r="K91" s="34" t="n">
+        <v>24904.82</v>
+      </c>
       <c r="L91" s="18" t="n">
-        <v>3166.68</v>
+        <v>-142.45</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>2111.12</v>
+        <v>-3448.12</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>4222.24</v>
+        <v>-5898.52</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>3166.68</v>
+        <v>-1932.02</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>12666.72</v>
+        <v>-11421.11</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>3166.65</v>
+        <v>-4312.73</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>3166.65</v>
+        <v>-2369.46</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>2111.1</v>
+        <v>-3383.22</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>3166.65</v>
+        <v>-5490.61</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>11611.05</v>
+        <v>-15556.02</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>3166.65</v>
+        <v>822.4400000000001</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>2111.1</v>
+        <v>4814.61</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>0</v>
+        <v>-3208.1</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>0</v>
+        <v>10600.17</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>5277.75</v>
+        <v>13029.12</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>0</v>
+        <v>-3668.49</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>0</v>
+        <v>1956</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -18586,41 +18084,79 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>단기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="n">
+        <v>35903.31</v>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="K92" s="9" t="n"/>
+      <c r="G92" s="18" t="n">
+        <v>25080.7</v>
+      </c>
+      <c r="H92" s="18" t="n">
+        <v>49587.95</v>
+      </c>
+      <c r="I92" s="18" t="n">
+        <v>24313.12</v>
+      </c>
+      <c r="J92" s="18" t="n">
+        <v>16811.79</v>
+      </c>
+      <c r="K92" s="34" t="n">
+        <v>115793.56</v>
+      </c>
+      <c r="L92" s="18" t="n">
+        <v>38170.09</v>
+      </c>
+      <c r="M92" s="18" t="n">
+        <v>45012.32</v>
+      </c>
+      <c r="N92" s="18" t="n">
+        <v>13885.79</v>
+      </c>
       <c r="O92" s="18" t="n">
-        <v>676.88</v>
-      </c>
-      <c r="P92" s="9" t="n"/>
+        <v>28973.09</v>
+      </c>
+      <c r="P92" s="34" t="n">
+        <v>126041.29</v>
+      </c>
       <c r="Q92" s="18" t="n">
-        <v>339.52</v>
+        <v>33877.28</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>458.35</v>
+        <v>44549.41</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>362.55</v>
+        <v>39577.06</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>480.41</v>
+        <v>41758.95</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>1640.83</v>
+        <v>159762.7</v>
       </c>
       <c r="V92" s="18" t="n">
-        <v>301.34</v>
+        <v>43254.36</v>
       </c>
       <c r="W92" s="18" t="n">
-        <v>282.28</v>
+        <v>62537.5</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>300.09</v>
-      </c>
-      <c r="Z92" s="9" t="n"/>
-      <c r="AB92" s="5" t="n"/>
+        <v>38286.3</v>
+      </c>
+      <c r="Y92" s="18" t="n">
+        <v>41720.63</v>
+      </c>
+      <c r="Z92" s="34" t="n">
+        <v>185798.79</v>
+      </c>
+      <c r="AA92" s="18" t="n">
+        <v>12615.31</v>
+      </c>
+      <c r="AB92" s="19" t="n">
+        <v>58442.97</v>
+      </c>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -18634,6 +18170,744 @@
       <c r="AM92" s="10" t="n"/>
       <c r="AN92" s="10" t="n"/>
       <c r="AO92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="n">
+        <v>1009.17</v>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="18" t="n">
+        <v>37980</v>
+      </c>
+      <c r="I93" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="18" t="n">
+        <v>425.39</v>
+      </c>
+      <c r="K93" s="34" t="n">
+        <v>38405.39</v>
+      </c>
+      <c r="L93" s="18" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="M93" s="18" t="n">
+        <v>92.59999999999999</v>
+      </c>
+      <c r="O93" s="18" t="n">
+        <v>850.95</v>
+      </c>
+      <c r="P93" s="9" t="n"/>
+      <c r="Q93" s="18" t="n">
+        <v>7868.45</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>1390.5</v>
+      </c>
+      <c r="U93" s="9" t="n"/>
+      <c r="V93" s="18" t="n">
+        <v>448.12</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>1049.57</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>2855.68</v>
+      </c>
+      <c r="Z93" s="9" t="n"/>
+      <c r="AA93" s="18" t="n">
+        <v>10424.53</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>264.77</v>
+      </c>
+      <c r="AC93" s="10" t="n"/>
+      <c r="AD93" s="10" t="n"/>
+      <c r="AE93" s="11" t="n"/>
+      <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="11" t="n"/>
+      <c r="AK93" s="10" t="n"/>
+      <c r="AL93" s="10" t="n"/>
+      <c r="AM93" s="10" t="n"/>
+      <c r="AN93" s="10" t="n"/>
+      <c r="AO93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="n">
+        <v>29610.48</v>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="18" t="n">
+        <v>22198.03</v>
+      </c>
+      <c r="H94" s="18" t="n">
+        <v>45469.65</v>
+      </c>
+      <c r="I94" s="18" t="n">
+        <v>33308.31</v>
+      </c>
+      <c r="J94" s="18" t="n">
+        <v>13492.38</v>
+      </c>
+      <c r="K94" s="34" t="n">
+        <v>114468.37</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>34146.04</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>46627.27</v>
+      </c>
+      <c r="N94" s="18" t="n">
+        <v>15474.67</v>
+      </c>
+      <c r="O94" s="18" t="n">
+        <v>28606.31</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>124854.29</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>40605.81</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>42783.88</v>
+      </c>
+      <c r="S94" s="18" t="n">
+        <v>40724.04</v>
+      </c>
+      <c r="T94" s="18" t="n">
+        <v>45413.19</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>169526.92</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>37121.93</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>56112.25</v>
+      </c>
+      <c r="X94" s="18" t="n">
+        <v>39784.46</v>
+      </c>
+      <c r="Y94" s="18" t="n">
+        <v>33840.8</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>166859.44</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>22701.02</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>56719.77</v>
+      </c>
+      <c r="AC94" s="10" t="n"/>
+      <c r="AD94" s="10" t="n"/>
+      <c r="AE94" s="11" t="n"/>
+      <c r="AF94" s="10" t="n"/>
+      <c r="AG94" s="10" t="n"/>
+      <c r="AH94" s="10" t="n"/>
+      <c r="AI94" s="10" t="n"/>
+      <c r="AJ94" s="11" t="n"/>
+      <c r="AK94" s="10" t="n"/>
+      <c r="AL94" s="10" t="n"/>
+      <c r="AM94" s="10" t="n"/>
+      <c r="AN94" s="10" t="n"/>
+      <c r="AO94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="18" t="n">
+        <v>800</v>
+      </c>
+      <c r="H95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="34" t="n">
+        <v>800</v>
+      </c>
+      <c r="L95" s="18" t="n">
+        <v>960</v>
+      </c>
+      <c r="M95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="34" t="n">
+        <v>960</v>
+      </c>
+      <c r="Q95" s="18" t="n">
+        <v>960</v>
+      </c>
+      <c r="R95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U95" s="34" t="n">
+        <v>960</v>
+      </c>
+      <c r="V95" s="18" t="n">
+        <v>1120</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>482.82</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z95" s="34" t="n">
+        <v>1602.82</v>
+      </c>
+      <c r="AA95" s="18" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="10" t="n"/>
+      <c r="AD95" s="10" t="n"/>
+      <c r="AE95" s="11" t="n"/>
+      <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="11" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="18" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="H96" s="18" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="I96" s="18" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="J96" s="18" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="K96" s="34" t="n">
+        <v>217.96</v>
+      </c>
+      <c r="L96" s="18" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="M96" s="18" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="P96" s="9" t="n"/>
+      <c r="Q96" s="18" t="n">
+        <v>27.69</v>
+      </c>
+      <c r="R96" s="18" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="U96" s="9" t="n"/>
+      <c r="V96" s="18" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="W96" s="18" t="n">
+        <v>30.41</v>
+      </c>
+      <c r="Z96" s="9" t="n"/>
+      <c r="AA96" s="18" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AB96" s="19" t="n">
+        <v>31.97</v>
+      </c>
+      <c r="AC96" s="10" t="n"/>
+      <c r="AD96" s="10" t="n"/>
+      <c r="AE96" s="11" t="n"/>
+      <c r="AF96" s="10" t="n"/>
+      <c r="AG96" s="10" t="n"/>
+      <c r="AH96" s="10" t="n"/>
+      <c r="AI96" s="10" t="n"/>
+      <c r="AJ96" s="11" t="n"/>
+      <c r="AK96" s="10" t="n"/>
+      <c r="AL96" s="10" t="n"/>
+      <c r="AM96" s="10" t="n"/>
+      <c r="AN96" s="10" t="n"/>
+      <c r="AO96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="n">
+        <v>10652.53</v>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="18" t="n">
+        <v>-7395.14</v>
+      </c>
+      <c r="H97" s="18" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="I97" s="18" t="n">
+        <v>3373.99</v>
+      </c>
+      <c r="J97" s="18" t="n">
+        <v>-3221.34</v>
+      </c>
+      <c r="K97" s="34" t="n">
+        <v>-7199.26</v>
+      </c>
+      <c r="L97" s="18" t="n">
+        <v>-7079.64</v>
+      </c>
+      <c r="M97" s="18" t="n">
+        <v>2191.22</v>
+      </c>
+      <c r="N97" s="18" t="n">
+        <v>5841.24</v>
+      </c>
+      <c r="O97" s="18" t="n">
+        <v>-3482.45</v>
+      </c>
+      <c r="P97" s="34" t="n">
+        <v>-2529.63</v>
+      </c>
+      <c r="Q97" s="18" t="n">
+        <v>-2304.96</v>
+      </c>
+      <c r="R97" s="18" t="n">
+        <v>4319.09</v>
+      </c>
+      <c r="S97" s="18" t="n">
+        <v>1708.19</v>
+      </c>
+      <c r="T97" s="18" t="n">
+        <v>-2864.64</v>
+      </c>
+      <c r="U97" s="34" t="n">
+        <v>857.6799999999999</v>
+      </c>
+      <c r="V97" s="18" t="n">
+        <v>781.54</v>
+      </c>
+      <c r="W97" s="18" t="n">
+        <v>7969.66</v>
+      </c>
+      <c r="X97" s="18" t="n">
+        <v>-5792.91</v>
+      </c>
+      <c r="Y97" s="18" t="n">
+        <v>5761.56</v>
+      </c>
+      <c r="Z97" s="34" t="n">
+        <v>8719.85</v>
+      </c>
+      <c r="AA97" s="18" t="n">
+        <v>737.0700000000001</v>
+      </c>
+      <c r="AB97" s="19" t="n">
+        <v>-4827.22</v>
+      </c>
+      <c r="AC97" s="10" t="n"/>
+      <c r="AD97" s="10" t="n"/>
+      <c r="AE97" s="11" t="n"/>
+      <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="11" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>10336.21</v>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>8499.120000000001</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>278.77</v>
+      </c>
+      <c r="I98" s="18" t="n">
+        <v>3674.61</v>
+      </c>
+      <c r="J98" s="18" t="n">
+        <v>-3796.73</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>8655.77</v>
+      </c>
+      <c r="L98" s="18" t="n">
+        <v>1695.22</v>
+      </c>
+      <c r="M98" s="18" t="n">
+        <v>2166.35</v>
+      </c>
+      <c r="N98" s="18" t="n">
+        <v>5846.85</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>-3582.29</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>6126.13</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>3892.15</v>
+      </c>
+      <c r="R98" s="18" t="n">
+        <v>4301.16</v>
+      </c>
+      <c r="S98" s="18" t="n">
+        <v>1681.46</v>
+      </c>
+      <c r="T98" s="18" t="n">
+        <v>-2890.96</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>6983.81</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>7769.05</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>7670.13</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>-5652.81</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>5917.29</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>15703.66</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>16440.73</v>
+      </c>
+      <c r="AB98" s="19" t="n">
+        <v>-4591.33</v>
+      </c>
+      <c r="AC98" s="10" t="n"/>
+      <c r="AD98" s="10" t="n"/>
+      <c r="AE98" s="11" t="n"/>
+      <c r="AF98" s="10" t="n"/>
+      <c r="AG98" s="10" t="n"/>
+      <c r="AH98" s="10" t="n"/>
+      <c r="AI98" s="10" t="n"/>
+      <c r="AJ98" s="11" t="n"/>
+      <c r="AK98" s="10" t="n"/>
+      <c r="AL98" s="10" t="n"/>
+      <c r="AM98" s="10" t="n"/>
+      <c r="AN98" s="10" t="n"/>
+      <c r="AO98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>3677.92</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>1819.2</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>112.42</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>5629.97</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="18" t="n">
+        <v>1296.7</v>
+      </c>
+      <c r="R99" s="18" t="n">
+        <v>902.0700000000001</v>
+      </c>
+      <c r="S99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="18" t="n">
+        <v>12.19</v>
+      </c>
+      <c r="U99" s="34" t="n">
+        <v>2210.96</v>
+      </c>
+      <c r="V99" s="18" t="n">
+        <v>1458.97</v>
+      </c>
+      <c r="X99" s="18" t="n">
+        <v>1369.53</v>
+      </c>
+      <c r="Y99" s="18" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Z99" s="9" t="n"/>
+      <c r="AA99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB99" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="10" t="n"/>
+      <c r="AD99" s="10" t="n"/>
+      <c r="AE99" s="11" t="n"/>
+      <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="11" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="I100" s="18" t="n">
+        <v>3166.68</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>4222.24</v>
+      </c>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="18" t="n">
+        <v>3166.68</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>2111.12</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>4222.24</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>3166.68</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>12666.72</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>3166.65</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>3166.65</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>2111.1</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>3166.65</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>11611.05</v>
+      </c>
+      <c r="V100" s="18" t="n">
+        <v>3166.65</v>
+      </c>
+      <c r="W100" s="18" t="n">
+        <v>2111.1</v>
+      </c>
+      <c r="X100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="34" t="n">
+        <v>5277.75</v>
+      </c>
+      <c r="AA100" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="10" t="n"/>
+      <c r="AD100" s="10" t="n"/>
+      <c r="AE100" s="11" t="n"/>
+      <c r="AF100" s="10" t="n"/>
+      <c r="AG100" s="10" t="n"/>
+      <c r="AH100" s="10" t="n"/>
+      <c r="AI100" s="10" t="n"/>
+      <c r="AJ100" s="11" t="n"/>
+      <c r="AK100" s="10" t="n"/>
+      <c r="AL100" s="10" t="n"/>
+      <c r="AM100" s="10" t="n"/>
+      <c r="AN100" s="10" t="n"/>
+      <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="O101" s="18" t="n">
+        <v>676.88</v>
+      </c>
+      <c r="P101" s="9" t="n"/>
+      <c r="Q101" s="18" t="n">
+        <v>339.52</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>458.35</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>480.41</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>1640.83</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>301.34</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>282.28</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>300.09</v>
+      </c>
+      <c r="Z101" s="9" t="n"/>
+      <c r="AB101" s="5" t="n"/>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18894,7 +19168,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4335</v>
+        <v>4270</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6510,7 +6510,7 @@
         <v>4120</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4220</v>
+        <v>4210</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4315</v>
+        <v>4300</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4335</v>
+        <v>4270</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08680556832600819</v>
+        <v>0.08680556832600821</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03995373376378768</v>
+        <v>0.03995373376378581</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03604608088321856</v>
+        <v>0.03604608088321742</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.87</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4270</v>
+        <v>4275</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6510,7 +6510,7 @@
         <v>4120</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4210</v>
+        <v>4175</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4300</v>
+        <v>4295</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4270</v>
+        <v>4275</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,280원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,250원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.8</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4275</v>
+        <v>4250</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6510,7 +6510,7 @@
         <v>4120</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4175</v>
+        <v>4155</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4295</v>
+        <v>4284</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4275</v>
+        <v>4250</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,265원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.81</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08680556832600821</v>
+        <v>0.08680556832600819</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03995373376378581</v>
+        <v>0.03995373376378768</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03604608088321742</v>
+        <v>0.03604608088321856</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-08</t>
+          <t>UPDATE: 26-10-09</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4250</v>
+        <v>4245</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4284</v>
+        <v>4283</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4250</v>
+        <v>4245</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,265원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,225원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="D52" s="36" t="n">
-        <v>0.08680556832600819</v>
+        <v>0.08680556832600821</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.03995373376378768</v>
+        <v>0.03995373376378581</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.03604608088321856</v>
+        <v>0.03604608088321742</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4245</v>
+        <v>4210</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4283</v>
+        <v>4270.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,7 +9638,7 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4245</v>
+        <v>4210</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.77</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="32">
@@ -41818,7 +41818,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4210</v>
+        <v>4200</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6510,7 +6510,7 @@
         <v>4120</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>4155</v>
+        <v>4000</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4270.8</v>
+        <v>4260.7</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4210</v>
+        <v>4200</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,225원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,250원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.73</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="32">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4260.7</v>
+        <v>4258.8</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,250원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,230원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4200</v>
+        <v>4240</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4258.8</v>
+        <v>4240</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4200</v>
+        <v>4240</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,230원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,070원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.72</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="32">
@@ -41818,7 +41818,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/155660_model.xlsx
+++ b/argus/kship/models/155660_model.xlsx
@@ -4489,7 +4489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5360,35 +5360,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5479,35 +5479,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -5598,35 +5598,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -5717,35 +5717,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -5836,35 +5836,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -5955,35 +5955,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6074,35 +6074,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6193,35 +6193,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6328,7 +6328,7 @@
         <v>4330</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>4240</v>
+        <v>4125</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -6601,7 +6601,7 @@
         <v>4461.5</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>4240</v>
+        <v>4221.9</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -9638,11 +9638,11 @@
         </is>
       </c>
       <c r="D44" s="34" t="n">
-        <v>4240</v>
+        <v>4125</v>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,070원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 4,245원)</t>
         </is>
       </c>
       <c r="F44" s="9" t="n"/>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="D45" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -10506,7 +10506,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -34363,7 +34363,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -39624,7 +39624,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -41808,7 +41808,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.77</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="32">
@@ -41818,7 +41818,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="33">
